--- a/resources/templates/standard/H3100-03.xlsx
+++ b/resources/templates/standard/H3100-03.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="58">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>■고객사명 : 제트에프삭스코리아</t>
   </si>
@@ -1099,7 +1102,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -1154,7 +1159,7 @@
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1174,12 +1179,12 @@
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
@@ -1196,30 +1201,30 @@
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M6" s="7"/>
       <c r="N6" s="7"/>
@@ -1229,29 +1234,29 @@
     <row r="7" ht="20.1" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="9"/>
       <c r="B7" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="10"/>
       <c r="D7" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="G7" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="13">
         <v>30</v>
       </c>
       <c r="K7" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M7" s="15"/>
       <c r="N7" s="15"/>
@@ -1267,7 +1272,7 @@
       <c r="F8" s="10"/>
       <c r="G8" s="11"/>
       <c r="H8" s="17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I8" s="17"/>
       <c r="J8" s="18">
@@ -1275,7 +1280,7 @@
       </c>
       <c r="K8" s="18"/>
       <c r="L8" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M8" s="19"/>
       <c r="N8" s="19"/>
@@ -1291,7 +1296,7 @@
       <c r="F9" s="10"/>
       <c r="G9" s="11"/>
       <c r="H9" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I9" s="17"/>
       <c r="J9" s="18">
@@ -1313,7 +1318,7 @@
       <c r="F10" s="10"/>
       <c r="G10" s="11"/>
       <c r="H10" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I10" s="17"/>
       <c r="J10" s="18">
@@ -1335,7 +1340,7 @@
       <c r="F11" s="10"/>
       <c r="G11" s="11"/>
       <c r="H11" s="20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I11" s="20"/>
       <c r="J11" s="21">
@@ -1353,29 +1358,29 @@
         <v>2</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" s="23"/>
       <c r="D12" s="24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E12" s="24"/>
       <c r="F12" s="24"/>
       <c r="G12" s="25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H12" s="26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I12" s="26"/>
       <c r="J12" s="26">
         <v>30</v>
       </c>
       <c r="K12" s="26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L12" s="27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M12" s="28"/>
       <c r="N12" s="28"/>
@@ -1391,7 +1396,7 @@
       <c r="F13" s="24"/>
       <c r="G13" s="25"/>
       <c r="H13" s="30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I13" s="30"/>
       <c r="J13" s="30">
@@ -1399,7 +1404,7 @@
       </c>
       <c r="K13" s="31"/>
       <c r="L13" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M13" s="19"/>
       <c r="N13" s="19"/>
@@ -1415,7 +1420,7 @@
       <c r="F14" s="24"/>
       <c r="G14" s="25"/>
       <c r="H14" s="30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I14" s="30"/>
       <c r="J14" s="30">
@@ -1437,7 +1442,7 @@
       <c r="F15" s="24"/>
       <c r="G15" s="25"/>
       <c r="H15" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I15" s="30"/>
       <c r="J15" s="30">
@@ -1459,7 +1464,7 @@
       <c r="F16" s="24"/>
       <c r="G16" s="25"/>
       <c r="H16" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I16" s="30"/>
       <c r="J16" s="30">
@@ -1477,12 +1482,12 @@
       <c r="B17" s="23"/>
       <c r="C17" s="23"/>
       <c r="D17" s="24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E17" s="24"/>
       <c r="F17" s="24"/>
       <c r="G17" s="26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H17" s="26"/>
       <c r="I17" s="26"/>
@@ -1490,10 +1495,10 @@
         <v>20</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L17" s="27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M17" s="28"/>
       <c r="N17" s="28"/>
@@ -1508,7 +1513,7 @@
       <c r="E18" s="24"/>
       <c r="F18" s="24"/>
       <c r="G18" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H18" s="30"/>
       <c r="I18" s="30"/>
@@ -1517,7 +1522,7 @@
       </c>
       <c r="K18" s="30"/>
       <c r="L18" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M18" s="19"/>
       <c r="N18" s="19"/>
@@ -1532,7 +1537,7 @@
       <c r="E19" s="24"/>
       <c r="F19" s="24"/>
       <c r="G19" s="30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H19" s="30"/>
       <c r="I19" s="30"/>
@@ -1554,7 +1559,7 @@
       <c r="E20" s="24"/>
       <c r="F20" s="24"/>
       <c r="G20" s="32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H20" s="32"/>
       <c r="I20" s="32"/>
@@ -1573,16 +1578,16 @@
         <v>3</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C21" s="24"/>
       <c r="D21" s="24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E21" s="24"/>
       <c r="F21" s="24"/>
       <c r="G21" s="26" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H21" s="26"/>
       <c r="I21" s="26"/>
@@ -1590,10 +1595,10 @@
         <v>20</v>
       </c>
       <c r="K21" s="26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L21" s="27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M21" s="28"/>
       <c r="N21" s="28"/>
@@ -1608,7 +1613,7 @@
       <c r="E22" s="24"/>
       <c r="F22" s="24"/>
       <c r="G22" s="30" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H22" s="30"/>
       <c r="I22" s="30"/>
@@ -1617,7 +1622,7 @@
       </c>
       <c r="K22" s="30"/>
       <c r="L22" s="19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M22" s="19"/>
       <c r="N22" s="19"/>
@@ -1632,7 +1637,7 @@
       <c r="E23" s="24"/>
       <c r="F23" s="24"/>
       <c r="G23" s="30" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H23" s="30"/>
       <c r="I23" s="30"/>
@@ -1654,7 +1659,7 @@
       <c r="E24" s="24"/>
       <c r="F24" s="24"/>
       <c r="G24" s="32" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H24" s="32"/>
       <c r="I24" s="32"/>
@@ -1670,7 +1675,7 @@
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="34" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B25" s="34"/>
       <c r="C25" s="34"/>
@@ -1695,7 +1700,7 @@
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="37" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B26" s="38"/>
       <c r="C26" s="38"/>
@@ -1706,7 +1711,7 @@
       <c r="H26" s="38"/>
       <c r="I26" s="38"/>
       <c r="J26" s="39" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K26" s="38"/>
       <c r="L26" s="38"/>
@@ -1771,7 +1776,7 @@
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="40" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B30" s="40"/>
       <c r="C30" s="40"/>
@@ -1783,12 +1788,12 @@
       <c r="G30" s="41"/>
       <c r="H30" s="41"/>
       <c r="I30" s="42" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J30" s="42"/>
       <c r="K30" s="42"/>
       <c r="L30" s="43" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M30" s="43"/>
       <c r="N30" s="43"/>
@@ -1797,7 +1802,7 @@
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="44" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B31" s="44"/>
       <c r="C31" s="44"/>
@@ -1817,34 +1822,34 @@
     </row>
     <row r="32" ht="20.1" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="45" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B32" s="45"/>
       <c r="C32" s="46" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D32" s="46"/>
       <c r="E32" s="46"/>
       <c r="F32" s="47" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G32" s="47"/>
       <c r="H32" s="46" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I32" s="46"/>
       <c r="J32" s="47" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K32" s="46" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L32" s="46"/>
       <c r="M32" s="47" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N32" s="46" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O32" s="46"/>
       <c r="P32" s="46"/>
